--- a/reports/daily_monitoring_report_500.xlsx
+++ b/reports/daily_monitoring_report_500.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17:22:15</t>
+          <t>17:38:56</t>
         </is>
       </c>
     </row>
